--- a/Outputs/PtX_demand_SK.xlsx
+++ b/Outputs/PtX_demand_SK.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,55 +488,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2030</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002929705966470399</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>0.0001895259569106624</v>
-      </c>
+        <v>0.008061202767657882</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.003717354300173964</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0008052079755571437</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>7.541896700914514e-11</v>
-      </c>
-      <c r="I2" t="n">
-        <v>7.787657911563706e-05</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2030</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
-        <v>3.699259365293863e-05</v>
-      </c>
+      <c r="C3" t="n">
+        <v>0.002929705966470399</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.0001895259569106624</v>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>7.541896700914514e-11</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7.787657911563706e-05</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -544,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.006592284555037041</v>
+        <v>3.699259365293863e-05</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -557,14 +561,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2030</v>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>0.006592284555037041</v>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -576,7 +582,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -584,24 +590,18 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>0.0005500310501749323</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6.470281442104808e-05</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>1.939025248945784e-05</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -609,14 +609,16 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.0005500310501749323</v>
+      </c>
       <c r="F7" t="n">
-        <v>0.0007299738205062158</v>
+        <v>6.470281442104808e-05</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>6.639032630352597e-05</v>
+        <v>1.939025248945784e-05</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -624,7 +626,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -633,17 +635,21 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.0007299738205062158</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>6.639032630352597e-05</v>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -652,29 +658,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0.003515587079057731</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.319298592853771e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.000206353572093</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0030691416041586</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.0001421047628064</v>
-      </c>
-      <c r="K9" t="n">
-        <v>7.395552156904465e-05</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -684,28 +678,28 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0.0338815414336028</v>
+        <v>0.003515587079057731</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003041955337624</v>
+        <v>4.319298592853771e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0018859603843858</v>
+        <v>0.000206353572093</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0198141550304741</v>
+        <v>0.0030691416041586</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0008601604282301</v>
+        <v>0.0001421047628064</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0005287307690825999</v>
+        <v>7.395552156904465e-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -713,20 +707,30 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
-        <v>0.002119495838650942</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.0338815414336028</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0003041955337624</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0018859603843858</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0198141550304741</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0008601604282301</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0005287307690825999</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -735,7 +739,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.00050465872964277</v>
+        <v>0.002119495838650942</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -747,102 +751,104 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2030</v>
       </c>
       <c r="C13" t="n">
-        <v>0.002929705966470399</v>
+        <v>0.02636735369823359</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00662927714868998</v>
+        <v>1.27897692436818e-20</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003174185618468644</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.03838133110449846</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.0003473885196909377</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.002092314031897767</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.02304695379254132</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.0010022651910365</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.0006026862906516446</v>
-      </c>
+        <v>0.009492208018359321</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2040</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.01184719247196035</v>
-      </c>
+        <v>2030</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>0.0009064259029022922</v>
-      </c>
+      <c r="E14" t="n">
+        <v>0.00050465872964277</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>6.313400547017451e-09</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.0001218731793767976</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2040</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>2030</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.03735826243236186</v>
+      </c>
       <c r="D15" t="n">
-        <v>3.600310459361152e-05</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+        <v>0.01034663144886394</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.01347160161238511</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.03838133110449846</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0003473885196909377</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.002092314031897767</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.02304695379254132</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.0010022651910365</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0006026862906516446</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2040</v>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>0.00801421731639082</v>
+      </c>
       <c r="D16" t="n">
-        <v>0.006415952138219271</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
+        <v>0.003457823638836334</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0007873406744893012</v>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -853,22 +859,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2040</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>0.01184719247196035</v>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>3.389392637646076e-10</v>
+        <v>0.0009064259029022922</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>6.313400547017451e-09</v>
+      </c>
       <c r="I17" t="n">
-        <v>4.145795003056843e-11</v>
+        <v>0.0001218731793767976</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -876,55 +886,49 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2040</v>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
-        <v>0.002078155952576548</v>
-      </c>
-      <c r="F18" t="n">
-        <v>7.782332623397337e-05</v>
-      </c>
+      <c r="D18" t="n">
+        <v>3.600310459361152e-05</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>2.861929870480182e-05</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2040</v>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>0.006415952138219271</v>
+      </c>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>0.000401207734482028</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>7.161271742331518e-05</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -933,17 +937,21 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>3.389392637646076e-10</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>4.145795003056843e-11</v>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -951,30 +959,24 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>0.002078155952576548</v>
+      </c>
       <c r="F21" t="n">
-        <v>0.001575216502142095</v>
-      </c>
-      <c r="G21" t="n">
-        <v>7.041169281899976e-05</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.0002512059842517</v>
-      </c>
+        <v>7.782332623397337e-05</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.0020866582874543</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.0001726342234394</v>
-      </c>
-      <c r="K21" t="n">
-        <v>9.71191615333176e-05</v>
-      </c>
+        <v>2.861929870480182e-05</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -984,28 +986,20 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.0093960001554407</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.0003270271112</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.0017781082385071</v>
-      </c>
+        <v>0.000401207734482028</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.0091304669370087</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.0007633154257556</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.0004665094298364</v>
-      </c>
+        <v>7.161271742331518e-05</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1013,9 +1007,7 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>0.001954838563554633</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1026,7 +1018,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1034,94 +1026,94 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>0.001946691550604262</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.001575216502142095</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7.041169281899976e-05</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0002512059842517</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0020866582874543</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0001726342234394</v>
+      </c>
+      <c r="K24" t="n">
+        <v>9.71191615333176e-05</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2040</v>
       </c>
-      <c r="C25" t="n">
-        <v>0.01184719247196035</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.006451955242812882</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.005979686066735442</v>
-      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0.01235667396014035</v>
+        <v>0.0093960001554407</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0003974388040189998</v>
+        <v>0.0003270271112</v>
       </c>
       <c r="H25" t="n">
-        <v>0.002029320536159347</v>
+        <v>0.0017781082385071</v>
       </c>
       <c r="I25" t="n">
-        <v>0.01143923046142586</v>
+        <v>0.0091304669370087</v>
       </c>
       <c r="J25" t="n">
-        <v>0.000935949649195</v>
+        <v>0.0007633154257556</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0005636285913697176</v>
+        <v>0.0004665094298364</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2050</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.02988984706647802</v>
-      </c>
+        <v>2040</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>0.0012593296311043</v>
-      </c>
+      <c r="E26" t="n">
+        <v>0.001954838563554633</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>1.07007053929174e-08</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.0001962837933709781</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2050</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="n">
-        <v>3.516486749315624e-05</v>
-      </c>
-      <c r="E27" t="inlineStr"/>
+        <v>2040</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.01777078870794052</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>0.006037271254771215</v>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1132,17 +1124,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="n">
-        <v>0.006266573656065958</v>
-      </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>0.001946691550604262</v>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1153,70 +1145,88 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2050</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+        <v>2040</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.03763219849629169</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.009909778881649216</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.01280429799599596</v>
+      </c>
       <c r="F29" t="n">
-        <v>3.774845040325875e-09</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+        <v>0.01235667396014035</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0003974388040189998</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.002029320536159347</v>
+      </c>
       <c r="I29" t="n">
-        <v>1.34907610501367e-09</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+        <v>0.01143923046142586</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.000935949649195</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.0005636285913697176</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2050</v>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>0.007974413997635115</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.003237964483256753</v>
+      </c>
       <c r="E30" t="n">
-        <v>0.0049398672685842</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.413917275720091e-05</v>
-      </c>
+        <v>0.0007722045448889857</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>7.875353694012995e-06</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>2050</v>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="n">
+        <v>0.02988984706647802</v>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>2.82976979993906e-05</v>
+        <v>0.0012593296311043</v>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>1.07007053929174e-08</v>
+      </c>
       <c r="I31" t="n">
-        <v>2.493561741812274e-05</v>
+        <v>0.0001962837933709781</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1224,69 +1234,49 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>2050</v>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>3.516486749315624e-05</v>
+      </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>7.20865110884525e-12</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2.592882074158322e-12</v>
-      </c>
-      <c r="H32" t="n">
-        <v>9.678283984348044e-12</v>
-      </c>
-      <c r="I32" t="n">
-        <v>3.255381781524249e-11</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1.182341707056067e-12</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1.636069195368075e-11</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2050</v>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0.006266573656065958</v>
+      </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>0.0001622105500796102</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.0001258133327862</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.000329025716349</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.0005427956238868</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.0002220349488531</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.0001318972613522</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1296,28 +1286,20 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>0.0004874016895610458</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.0002949646045886</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.0016125152633203</v>
-      </c>
+        <v>3.774845040325875e-09</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.0015959837096004</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.0006570244378383</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.0003828919678056</v>
-      </c>
+        <v>1.34907610501367e-09</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1326,19 +1308,23 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>0.001821783139629031</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>0.0049398672685842</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.413917275720091e-05</v>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>7.875353694012995e-06</v>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1346,50 +1332,206 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
-        <v>0.004708618200607745</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>2.82976979993906e-05</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>2.493561741812274e-05</v>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>2050</v>
       </c>
-      <c r="C37" t="n">
-        <v>0.02988984706647802</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.006301738523559114</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.01147026860882098</v>
-      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
+        <v>7.20865110884525e-12</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.592882074158322e-12</v>
+      </c>
+      <c r="H37" t="n">
+        <v>9.678283984348044e-12</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.255381781524249e-11</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.182341707056067e-12</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.636069195368075e-11</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Biogenic Liquids</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0.0001622105500796102</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.0001258133327862</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.000329025716349</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0005427956238868</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.0002220349488531</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.0001318972613522</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Fossil Liquids</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0.0004874016895610458</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0002949646045886</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0016125152633203</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.0015959837096004</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.0006570244378383</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.0003828919678056</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Biomass [Solid]</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>0.001821783139629031</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Fossil Rest</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Renewable Energy Carrier</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>0.004708618200607745</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Overall Demand</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.03786426106411313</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.009539703006815867</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.01224247315370996</v>
+      </c>
+      <c r="F43" t="n">
         <v>0.001951382523555239</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G43" t="n">
         <v>0.000420777939967682</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H43" t="n">
         <v>0.001941551690052977</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I43" t="n">
         <v>0.002367875479600236</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J43" t="n">
         <v>0.0008790593878737417</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K43" t="n">
         <v>0.000514789245518492</v>
       </c>
     </row>

--- a/Outputs/PtX_demand_SK.xlsx
+++ b/Outputs/PtX_demand_SK.xlsx
@@ -503,11 +503,19 @@
       <c r="E2" t="n">
         <v>0.0008052079755571437</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.00408407370820503</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0017490095903823</v>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0.001314333377595</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0012877742694912</v>
+      </c>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -730,16 +738,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2030</v>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>0.02636735369823359</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.27897692436818e-20</v>
+      </c>
       <c r="E12" t="n">
-        <v>0.002119495838650942</v>
+        <v>0.009492208018359321</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -751,20 +763,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2030</v>
       </c>
-      <c r="C13" t="n">
-        <v>0.02636735369823359</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.27897692436818e-20</v>
-      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.009492208018359321</v>
+        <v>0.002119495838650942</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -813,19 +821,19 @@
         <v>0.01347160161238511</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03838133110449846</v>
+        <v>0.04246540481270349</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003473885196909377</v>
+        <v>0.002096398110073238</v>
       </c>
       <c r="H15" t="n">
         <v>0.002092314031897767</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02304695379254132</v>
+        <v>0.02436128717013632</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0010022651910365</v>
+        <v>0.0022900394605277</v>
       </c>
       <c r="K15" t="n">
         <v>0.0006026862906516446</v>
@@ -849,11 +857,19 @@
       <c r="E16" t="n">
         <v>0.0007873406744893012</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.01165675673348584</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0020526240769976</v>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0.0049383647000153</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.0012700446922534</v>
+      </c>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1080,16 +1096,18 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2040</v>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="n">
+        <v>0.01777078870794052</v>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>0.001954838563554633</v>
+        <v>0.006037271254771215</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1101,18 +1119,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2040</v>
       </c>
-      <c r="C27" t="n">
-        <v>0.01777078870794052</v>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>0.006037271254771215</v>
+        <v>0.001954838563554633</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1161,19 +1177,19 @@
         <v>0.01280429799599596</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01235667396014035</v>
+        <v>0.02401343069362619</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0003974388040189998</v>
+        <v>0.0024500628810166</v>
       </c>
       <c r="H29" t="n">
         <v>0.002029320536159347</v>
       </c>
       <c r="I29" t="n">
-        <v>0.01143923046142586</v>
+        <v>0.01637759516144116</v>
       </c>
       <c r="J29" t="n">
-        <v>0.000935949649195</v>
+        <v>0.0022059943414484</v>
       </c>
       <c r="K29" t="n">
         <v>0.0005636285913697176</v>
@@ -1197,11 +1213,19 @@
       <c r="E30" t="n">
         <v>0.0007722045448889857</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.01362990097853559</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0023050848418919</v>
+      </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.007646782207488201</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.0012971272023691</v>
+      </c>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1440,7 +1464,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1448,9 +1472,7 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
-        <v>0.001821783139629031</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -1461,7 +1483,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1469,7 +1491,9 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>0.001821783139629031</v>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1517,19 +1541,19 @@
         <v>0.01224247315370996</v>
       </c>
       <c r="F43" t="n">
-        <v>0.001951382523555239</v>
+        <v>0.01558128350209083</v>
       </c>
       <c r="G43" t="n">
-        <v>0.000420777939967682</v>
+        <v>0.002725862781859582</v>
       </c>
       <c r="H43" t="n">
         <v>0.001941551690052977</v>
       </c>
       <c r="I43" t="n">
-        <v>0.002367875479600236</v>
+        <v>0.01001465768708844</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0008790593878737417</v>
+        <v>0.002176186590242842</v>
       </c>
       <c r="K43" t="n">
         <v>0.000514789245518492</v>
